--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62298.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62298.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>IG.1103</t>
+          <t>16.1103</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aidie</t>
+          <t>Jade</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KIAIM</t>
+          <t>KAM</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62298.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62298.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>17/11/2025</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G05D</t>
+          <t>G05C</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62298.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62298.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KAM</t>
+          <t>RAM</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62298.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62298.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jade</t>
+          <t>JADE</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62298.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62298.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
